--- a/data/trans_dic/P79A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P79A_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,04</t>
+          <t>0,85; 8,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 12,79</t>
+          <t>2,97; 10,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,35</t>
+          <t>2,49; 7,54</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,9</t>
+          <t>1,44; 6,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,32</t>
+          <t>0,96; 3,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,15</t>
+          <t>1,4; 4,24</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,62</t>
+          <t>1,87; 4,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,14</t>
+          <t>2,05; 4,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,86</t>
+          <t>2,19; 4,07</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,97</t>
+          <t>1,41; 4,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,41</t>
+          <t>1,05; 2,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,39</t>
+          <t>1,5; 2,9</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,86</t>
+          <t>1,57; 4,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,45</t>
+          <t>1,55; 3,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,17</t>
+          <t>1,75; 3,46</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,35</t>
+          <t>0,5; 2,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,24</t>
+          <t>0,38; 1,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,4</t>
+          <t>0,53; 1,67</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,16</t>
+          <t>0,22; 1,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,96</t>
+          <t>0,16; 1,05</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,77</t>
+          <t>1,88; 3,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,58</t>
+          <t>1,81; 2,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,52</t>
+          <t>1,94; 2,78</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30229</t>
+          <t>33677</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1922; 24175</t>
+          <t>3473; 32849</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10812; 40066</t>
+          <t>10766; 36286</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15259; 52396</t>
+          <t>19190; 58060</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14350</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22287</t>
+          <t>24658</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5560; 29231</t>
+          <t>6860; 29629</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2891; 16992</t>
+          <t>4794; 19908</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12367; 38818</t>
+          <t>13668; 41506</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>18968</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31110</t>
+          <t>37526</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8823; 24803</t>
+          <t>11591; 28384</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9926; 24537</t>
+          <t>12752; 27768</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21713; 43583</t>
+          <t>27237; 50583</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>18086</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>30827</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4306; 26356</t>
+          <t>9880; 28463</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6508; 17196</t>
+          <t>7767; 18943</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14599; 38311</t>
+          <t>21619; 41632</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>16217</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>30589</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7691; 21672</t>
+          <t>9544; 27107</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7853; 18880</t>
+          <t>9436; 21915</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17359; 35123</t>
+          <t>21288; 42170</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>8573</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1879; 8667</t>
+          <t>2028; 9804</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>558; 7534</t>
+          <t>1689; 7829</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3499; 13666</t>
+          <t>4453; 14132</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>3791</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4724</t>
+          <t>0; 5884</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>647; 4939</t>
+          <t>1034; 6483</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1095; 6795</t>
+          <t>1235; 8112</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>84279</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145352</t>
+          <t>169641</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>51781; 95956</t>
+          <t>66461; 111769</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>54238; 95737</t>
+          <t>67586; 106853</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>115676; 180662</t>
+          <t>141286; 202044</t>
         </is>
       </c>
     </row>
